--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.59036155768423</v>
+        <v>6.270933753123688</v>
       </c>
       <c r="D2" t="n">
-        <v>22.20618323159091</v>
+        <v>3.608504775133522</v>
       </c>
       <c r="E2" t="n">
-        <v>12.69385251595086</v>
+        <v>2.062751033842015</v>
       </c>
       <c r="F2" t="n">
-        <v>9.225941899482203</v>
+        <v>1.499215558665858</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.34688683632084</v>
+        <v>2.981369110902137</v>
       </c>
       <c r="D3" t="n">
-        <v>17.64279913608631</v>
+        <v>2.866954859614026</v>
       </c>
       <c r="E3" t="n">
-        <v>12.69385251595086</v>
+        <v>2.062751033842015</v>
       </c>
       <c r="F3" t="n">
-        <v>9.225941899482203</v>
+        <v>1.499215558665858</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.60550291430741</v>
+        <v>2.210894223574954</v>
       </c>
       <c r="D4" t="n">
-        <v>7.438750132750681</v>
+        <v>1.208796896571986</v>
       </c>
       <c r="E4" t="n">
-        <v>12.69385251595086</v>
+        <v>2.062751033842015</v>
       </c>
       <c r="F4" t="n">
-        <v>9.225941899482203</v>
+        <v>1.499215558665858</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.44044725761982</v>
+        <v>7.22157267936322</v>
       </c>
       <c r="D5" t="n">
-        <v>35.78339409509322</v>
+        <v>5.814801540452649</v>
       </c>
       <c r="E5" t="n">
-        <v>12.69385251595086</v>
+        <v>2.062751033842015</v>
       </c>
       <c r="F5" t="n">
-        <v>9.225941899482203</v>
+        <v>1.499215558665858</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.91293488954308</v>
+        <v>5.348351919550751</v>
       </c>
       <c r="D6" t="n">
-        <v>28.02502517571498</v>
+        <v>4.554066591053685</v>
       </c>
       <c r="E6" t="n">
-        <v>12.69385251595086</v>
+        <v>2.062751033842015</v>
       </c>
       <c r="F6" t="n">
-        <v>9.225941899482203</v>
+        <v>1.499215558665858</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.45737395383109</v>
+        <v>7.224323267497553</v>
       </c>
       <c r="D7" t="n">
-        <v>7.310570733153773</v>
+        <v>1.187967744137488</v>
       </c>
       <c r="E7" t="n">
-        <v>12.69385251595086</v>
+        <v>2.062751033842015</v>
       </c>
       <c r="F7" t="n">
-        <v>9.225941899482203</v>
+        <v>1.499215558665858</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.82586289691824</v>
+        <v>5.659202720749214</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11107061733047</v>
+        <v>3.918048975316202</v>
       </c>
       <c r="E8" t="n">
-        <v>12.69385251595086</v>
+        <v>2.062751033842015</v>
       </c>
       <c r="F8" t="n">
-        <v>9.225941899482203</v>
+        <v>1.499215558665858</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>53.92969561925675</v>
+        <v>8.763575538129222</v>
       </c>
       <c r="D9" t="n">
-        <v>15.32245991274828</v>
+        <v>2.489899735821595</v>
       </c>
       <c r="E9" t="n">
-        <v>12.69385251595086</v>
+        <v>2.062751033842015</v>
       </c>
       <c r="F9" t="n">
-        <v>9.225941899482203</v>
+        <v>1.499215558665858</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
